--- a/NECP Scenario/Results/Regional Results/EL54_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL54_Generation.xlsx
@@ -537,25 +537,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.547324591738688E-12</v>
+        <v>2.284565011464032E-12</v>
       </c>
       <c r="C2">
-        <v>8.102396633850434E-13</v>
+        <v>1.196285802041038E-12</v>
       </c>
       <c r="D2">
-        <v>1.190475611932521E-12</v>
+        <v>1.75769264349923E-12</v>
       </c>
       <c r="E2">
-        <v>1.749236105384498E-12</v>
+        <v>2.582683201764605E-12</v>
       </c>
       <c r="F2">
-        <v>2.57022239207502E-12</v>
+        <v>3.794836713682937E-12</v>
       </c>
       <c r="G2">
-        <v>3.776446695371545E-12</v>
+        <v>5.57578134514818E-12</v>
       </c>
       <c r="H2">
-        <v>2.288757318855199E-11</v>
+        <v>3.379279957979737E-11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5.367213009187527E-08</v>
+        <v>7.836689411356179E-08</v>
       </c>
       <c r="C3">
-        <v>4.686186102140974E-08</v>
+        <v>6.897913651049292E-08</v>
       </c>
       <c r="D3">
-        <v>1.369830336015385E-07</v>
+        <v>1.955069733705554E-07</v>
       </c>
       <c r="E3">
-        <v>2.631708349412779E-07</v>
+        <v>3.530933300384581E-07</v>
       </c>
       <c r="F3">
-        <v>7.86653721063189E-07</v>
+        <v>1.002646810985734E-06</v>
       </c>
       <c r="G3">
-        <v>3.086322344140398E-06</v>
+        <v>4.283756603329642E-06</v>
       </c>
       <c r="H3">
-        <v>2.091586621401024</v>
+        <v>1.298376506583138</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4.562131058058504E-08</v>
+        <v>6.661185999862984E-08</v>
       </c>
       <c r="C4">
-        <v>3.983258187372098E-08</v>
+        <v>5.863226603744339E-08</v>
       </c>
       <c r="D4">
-        <v>1.164355785668598E-07</v>
+        <v>1.661809273685168E-07</v>
       </c>
       <c r="E4">
-        <v>2.236952097057126E-07</v>
+        <v>3.001293305362921E-07</v>
       </c>
       <c r="F4">
-        <v>6.686556629093056E-07</v>
+        <v>8.522497893414533E-07</v>
       </c>
       <c r="G4">
-        <v>2.623373992524951E-06</v>
+        <v>3.641193112833788E-06</v>
       </c>
       <c r="H4">
-        <v>1.777848628189713</v>
+        <v>1.10362003059599</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -618,22 +618,22 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.3603880137085929</v>
+        <v>0.360323042260781</v>
       </c>
       <c r="D5">
-        <v>0.3552822567921737</v>
+        <v>0.3548313969027034</v>
       </c>
       <c r="E5">
-        <v>0.3908224341145952</v>
+        <v>0.3900989034233326</v>
       </c>
       <c r="F5">
-        <v>0.4054627768713241</v>
+        <v>0.4058532360873507</v>
       </c>
       <c r="G5">
-        <v>0.4201553822817241</v>
+        <v>0.4203184218041458</v>
       </c>
       <c r="H5">
-        <v>0.4352842886936002</v>
+        <v>0.4355964301737056</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -667,25 +667,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.1863185604184021</v>
+        <v>0.1864599034315225</v>
       </c>
       <c r="C7">
-        <v>1.212624999653988</v>
+        <v>1.212624998846358</v>
       </c>
       <c r="D7">
-        <v>1.175328480293604</v>
+        <v>1.173470467621578</v>
       </c>
       <c r="E7">
-        <v>1.270638889533974</v>
+        <v>1.270638889397641</v>
       </c>
       <c r="F7">
-        <v>1.303972222971562</v>
+        <v>1.303972222853121</v>
       </c>
       <c r="G7">
-        <v>1.335472222778918</v>
+        <v>1.335472222563682</v>
       </c>
       <c r="H7">
-        <v>1.36697222043158</v>
+        <v>1.36697221924805</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -719,25 +719,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.06514634979291518</v>
+        <v>0.06519577042509844</v>
       </c>
       <c r="C9">
-        <v>0.06360674141323865</v>
+        <v>0.06367171257772186</v>
       </c>
       <c r="D9">
-        <v>0.05567175729373665</v>
+        <v>0.05547296240130126</v>
       </c>
       <c r="E9">
-        <v>0.05345689788603906</v>
+        <v>0.054180428527667</v>
       </c>
       <c r="F9">
-        <v>0.05047156681883878</v>
+        <v>0.05008110755845144</v>
       </c>
       <c r="G9">
-        <v>0.04679294735215936</v>
+        <v>0.0466299077501524</v>
       </c>
       <c r="H9">
-        <v>0.0426780260875275</v>
+        <v>0.04236588416734031</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -748,22 +748,22 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>1.159838851811942E-07</v>
+        <v>1.676051680872327E-07</v>
       </c>
       <c r="D10">
-        <v>1.233382517250461E-07</v>
+        <v>1.855751127051105E-07</v>
       </c>
       <c r="E10">
-        <v>1.196690753378693E-07</v>
+        <v>1.764285709200471E-07</v>
       </c>
       <c r="F10">
-        <v>9.180358620596064E-08</v>
+        <v>1.366150151271428E-07</v>
       </c>
       <c r="G10">
-        <v>8.741411839161567E-08</v>
+        <v>1.301524555178662E-07</v>
       </c>
       <c r="H10">
-        <v>4.368117242282789E-07</v>
+        <v>6.46670149027436E-07</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.29452129953754</v>
+        <v>1.294521301963608</v>
       </c>
       <c r="C14">
-        <v>1.314994376914167</v>
+        <v>1.314994375108566</v>
       </c>
       <c r="D14">
-        <v>1.445293990295573</v>
+        <v>1.445293976551037</v>
       </c>
       <c r="E14">
-        <v>1.724845786867972</v>
+        <v>1.724845460517558</v>
       </c>
       <c r="F14">
-        <v>1.761190882561956</v>
+        <v>1.745319209320335</v>
       </c>
       <c r="G14">
-        <v>1.975546799278079</v>
+        <v>1.960258860868406</v>
       </c>
       <c r="H14">
-        <v>2.271235179139038</v>
+        <v>2.251771856364412</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -979,25 +979,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>4.554602959332644E-08</v>
+        <v>6.646251329587541E-08</v>
       </c>
       <c r="C19">
-        <v>4.338101198845677E-08</v>
+        <v>6.396520137089948E-08</v>
       </c>
       <c r="D19">
-        <v>1.056686866396276E-07</v>
+        <v>1.535137968569084E-07</v>
       </c>
       <c r="E19">
-        <v>2.236732882316507E-07</v>
+        <v>3.135042075989525E-07</v>
       </c>
       <c r="F19">
-        <v>6.209563146291846E-07</v>
+        <v>8.23589373005479E-07</v>
       </c>
       <c r="G19">
-        <v>1.147910743192542E-06</v>
+        <v>1.711338136327311E-06</v>
       </c>
       <c r="H19">
-        <v>9.141059199728986E-06</v>
+        <v>1.361341626195165E-05</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1031,25 +1031,25 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>3.643682367853559E-08</v>
+        <v>5.317001064006523E-08</v>
       </c>
       <c r="C21">
-        <v>3.470480959076549E-08</v>
+        <v>5.117216109671957E-08</v>
       </c>
       <c r="D21">
-        <v>8.453494931170213E-08</v>
+        <v>1.228110374855267E-07</v>
       </c>
       <c r="E21">
-        <v>1.789386305853206E-07</v>
+        <v>2.508033660791618E-07</v>
       </c>
       <c r="F21">
-        <v>4.96765051703348E-07</v>
+        <v>6.58871498404383E-07</v>
       </c>
       <c r="G21">
-        <v>9.183285945540331E-07</v>
+        <v>1.369070509061849E-06</v>
       </c>
       <c r="H21">
-        <v>7.312847359783188E-06</v>
+        <v>1.089073300956132E-05</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1060,22 +1060,22 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>1.424683446509632E-08</v>
+        <v>2.120299043172549E-08</v>
       </c>
       <c r="D22">
-        <v>2.118370204727468E-08</v>
+        <v>3.282504677400545E-08</v>
       </c>
       <c r="E22">
-        <v>5.322851429568548E-08</v>
+        <v>8.392408061643812E-08</v>
       </c>
       <c r="F22">
-        <v>2.738886225372714E-07</v>
+        <v>3.66813148397401E-07</v>
       </c>
       <c r="G22">
-        <v>0.2256956076753258</v>
+        <v>0.2376759779495457</v>
       </c>
       <c r="H22">
-        <v>0.4509409583405055</v>
+        <v>0.4509409576205822</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1083,25 +1083,25 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.7396090045079755</v>
+        <v>0.7396090043749957</v>
       </c>
       <c r="C23">
-        <v>0.7396090046197891</v>
+        <v>0.7396090045428059</v>
       </c>
       <c r="D23">
-        <v>0.7396090045451779</v>
+        <v>0.7396090044273658</v>
       </c>
       <c r="E23">
-        <v>0.7396090044752966</v>
+        <v>0.7396090043199326</v>
       </c>
       <c r="F23">
-        <v>0.7396090043626207</v>
+        <v>0.7396090041507539</v>
       </c>
       <c r="G23">
-        <v>0.7396090041870222</v>
+        <v>0.7396090038690721</v>
       </c>
       <c r="H23">
-        <v>0.7396090010424069</v>
+        <v>0.7396089993439107</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1109,25 +1109,25 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>1.275920058402022E-08</v>
+        <v>1.886121194486742E-08</v>
       </c>
       <c r="C24">
-        <v>2.020469768112894E-07</v>
+        <v>2.921702136289486E-07</v>
       </c>
       <c r="D24">
-        <v>2.138609368112712E-07</v>
+        <v>3.215273460905152E-07</v>
       </c>
       <c r="E24">
-        <v>2.088038049504888E-07</v>
+        <v>3.078415919775622E-07</v>
       </c>
       <c r="F24">
-        <v>1.62940905401596E-07</v>
+        <v>2.422970564173258E-07</v>
       </c>
       <c r="G24">
-        <v>1.580136520859429E-07</v>
+        <v>2.350386328171476E-07</v>
       </c>
       <c r="H24">
-        <v>7.943347537835219E-07</v>
+        <v>1.175864270497392E-06</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1135,25 +1135,25 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>4.577109647195719E-09</v>
+        <v>6.766060604337625E-09</v>
       </c>
       <c r="C25">
-        <v>2.581334971241985E-09</v>
+        <v>3.801035557750801E-09</v>
       </c>
       <c r="D25">
-        <v>2.827186320549707E-09</v>
+        <v>4.164621491586124E-09</v>
       </c>
       <c r="E25">
-        <v>3.638172888303745E-09</v>
+        <v>5.364166217437321E-09</v>
       </c>
       <c r="F25">
-        <v>4.103423591917164E-09</v>
+        <v>6.042179098609564E-09</v>
       </c>
       <c r="G25">
-        <v>4.926533306976531E-09</v>
+        <v>7.252522186251771E-09</v>
       </c>
       <c r="H25">
-        <v>2.785949580883494E-08</v>
+        <v>4.121078130244672E-08</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1190,22 +1190,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>8.892426923571856E-09</v>
+        <v>1.312194548417074E-08</v>
       </c>
       <c r="D27">
-        <v>2.952726947051155E-08</v>
+        <v>4.422116569280549E-08</v>
       </c>
       <c r="E27">
-        <v>8.437727702186684E-08</v>
+        <v>1.26037010925566E-07</v>
       </c>
       <c r="F27">
-        <v>2.390923615734205E-07</v>
+        <v>3.571204657072697E-07</v>
       </c>
       <c r="G27">
-        <v>6.163373219806055E-07</v>
+        <v>1.148030259237963E-06</v>
       </c>
       <c r="H27">
-        <v>0.7760006333772372</v>
+        <v>1.137398999225498</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1268,22 +1268,22 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0.2312682823592341</v>
+        <v>0.1661786213030687</v>
       </c>
       <c r="D30">
-        <v>0.4294442129664864</v>
+        <v>0.3593788164688828</v>
       </c>
       <c r="E30">
-        <v>0.5137296731937611</v>
+        <v>0.4344428327729368</v>
       </c>
       <c r="F30">
-        <v>0.6502420039175969</v>
+        <v>0.5568769689827792</v>
       </c>
       <c r="G30">
-        <v>1.154005556395524</v>
+        <v>1.051607165451562</v>
       </c>
       <c r="H30">
-        <v>3.068780801878654</v>
+        <v>2.669607760443783</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.36134930544424</v>
+        <v>0.3613493026792625</v>
       </c>
       <c r="C31">
-        <v>0.361202361245955</v>
+        <v>0.3612672228337037</v>
       </c>
       <c r="D31">
-        <v>0.3574511446370953</v>
+        <v>0.3576702472915261</v>
       </c>
       <c r="E31">
-        <v>0.3522109459088407</v>
+        <v>0.3525151781627069</v>
       </c>
       <c r="F31">
-        <v>0.3446975831613765</v>
+        <v>0.3460035573977331</v>
       </c>
       <c r="G31">
-        <v>0.3280244543467519</v>
+        <v>0.3270582648300246</v>
       </c>
       <c r="H31">
-        <v>0.2968826955492165</v>
+        <v>0.306890822060926</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1320,22 +1320,22 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>8.218603029119896E-09</v>
+        <v>1.221513826543683E-08</v>
       </c>
       <c r="D32">
-        <v>3.06019266985533E-08</v>
+        <v>4.921966234021919E-08</v>
       </c>
       <c r="E32">
-        <v>1.716156667686739E-07</v>
+        <v>5.047604050481651E-07</v>
       </c>
       <c r="F32">
-        <v>0.3262701735291214</v>
+        <v>0.3422233150903423</v>
       </c>
       <c r="G32">
-        <v>0.498465775076632</v>
+        <v>0.5138107468231166</v>
       </c>
       <c r="H32">
-        <v>0.8238652846443622</v>
+        <v>0.8434142480475332</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.006954586383311808</v>
+        <v>0.006954583972643221</v>
       </c>
       <c r="C33">
-        <v>0.006954587194204892</v>
+        <v>0.00695458501088889</v>
       </c>
       <c r="D33">
-        <v>0.006954581110620664</v>
+        <v>0.006954576249911549</v>
       </c>
       <c r="E33">
-        <v>0.006954576785213328</v>
+        <v>0.006954570010808211</v>
       </c>
       <c r="F33">
-        <v>0.006809358755033681</v>
+        <v>0.006727899414456985</v>
       </c>
       <c r="G33">
-        <v>0.006418561758379238</v>
+        <v>0.006361528459941667</v>
       </c>
       <c r="H33">
-        <v>0.006030726226442886</v>
+        <v>0.005945085830483096</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>3.010185947469402E-08</v>
+        <v>4.434971224870815E-08</v>
       </c>
       <c r="D34">
-        <v>3.088347687976364E-08</v>
+        <v>4.651822335398228E-08</v>
       </c>
       <c r="E34">
-        <v>6.563781984220265E-08</v>
+        <v>9.746708047286324E-08</v>
       </c>
       <c r="F34">
-        <v>1.185985028385288E-07</v>
+        <v>1.7468595790111E-07</v>
       </c>
       <c r="G34">
-        <v>1.543728716443983E-07</v>
+        <v>2.319079903722062E-07</v>
       </c>
       <c r="H34">
-        <v>9.276813185742272E-07</v>
+        <v>1.383126612248941E-06</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1395,25 +1395,25 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.1771987840947093</v>
+        <v>0.1771987840879911</v>
       </c>
       <c r="C35">
-        <v>0.1771987815950571</v>
+        <v>0.177198780391051</v>
       </c>
       <c r="D35">
-        <v>0.177198632045702</v>
+        <v>0.1771985807719289</v>
       </c>
       <c r="E35">
-        <v>0.1771985208642515</v>
+        <v>0.1771984020905244</v>
       </c>
       <c r="F35">
-        <v>0.1771983592045008</v>
+        <v>0.1771981359811814</v>
       </c>
       <c r="G35">
-        <v>0.1771979372163167</v>
+        <v>0.1771970757064763</v>
       </c>
       <c r="H35">
-        <v>0.1771778619910174</v>
+        <v>0.1771907007469799</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1424,22 +1424,22 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>5.076601812873056E-08</v>
+        <v>7.448117054718486E-08</v>
       </c>
       <c r="D36">
-        <v>5.892363750049171E-08</v>
+        <v>8.841840297655499E-08</v>
       </c>
       <c r="E36">
-        <v>1.767652191619338E-07</v>
+        <v>2.614179781729799E-07</v>
       </c>
       <c r="F36">
-        <v>2.256052497843596E-07</v>
+        <v>3.430041111260105E-07</v>
       </c>
       <c r="G36">
-        <v>2.165427873330201E-07</v>
+        <v>3.359620740790676E-07</v>
       </c>
       <c r="H36">
-        <v>1.046608549007104E-06</v>
+        <v>1.551138320537445E-06</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.2149339016265536</v>
+        <v>0.2149338964321808</v>
       </c>
       <c r="C37">
-        <v>0.2076396522457517</v>
+        <v>0.2075597936366511</v>
       </c>
       <c r="D37">
-        <v>0.1932428364421224</v>
+        <v>0.192708916496744</v>
       </c>
       <c r="E37">
-        <v>0.1902041571089144</v>
+        <v>0.1894339499310908</v>
       </c>
       <c r="F37">
-        <v>0.1911429533928184</v>
+        <v>0.1898809738909056</v>
       </c>
       <c r="G37">
-        <v>0.192656810072236</v>
+        <v>0.1926931478076265</v>
       </c>
       <c r="H37">
-        <v>0.1895844760838399</v>
+        <v>0.1933434181671945</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.003616323805987505</v>
+        <v>0.003616334182724818</v>
       </c>
       <c r="C38">
-        <v>0.01121161367140262</v>
+        <v>0.01115837154720467</v>
       </c>
       <c r="D38">
-        <v>0.03351664451281635</v>
+        <v>0.0334019395316725</v>
       </c>
       <c r="E38">
-        <v>0.04815077678773506</v>
+        <v>0.04770429971984536</v>
       </c>
       <c r="F38">
-        <v>0.06605787746371418</v>
+        <v>0.06441531369186823</v>
       </c>
       <c r="G38">
-        <v>0.1309553009991071</v>
+        <v>0.1344032416890895</v>
       </c>
       <c r="H38">
-        <v>0.6018789819538168</v>
+        <v>0.6454193381658777</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>9.921815968520171E-08</v>
+        <v>1.448294074094372E-07</v>
       </c>
       <c r="C40">
-        <v>9.024287300986652E-08</v>
+        <v>1.329443378813924E-07</v>
       </c>
       <c r="D40">
-        <v>2.426517202411661E-07</v>
+        <v>3.490207702274638E-07</v>
       </c>
       <c r="E40">
-        <v>4.868441231729286E-07</v>
+        <v>6.665975376374105E-07</v>
       </c>
       <c r="F40">
-        <v>1.407610035692374E-06</v>
+        <v>1.826236183991213E-06</v>
       </c>
       <c r="G40">
-        <v>4.234233087332939E-06</v>
+        <v>5.995094739656953E-06</v>
       </c>
       <c r="H40">
-        <v>2.091595762460224</v>
+        <v>1.2983901199994</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>8.205813425912063E-08</v>
+        <v>1.197818706386951E-07</v>
       </c>
       <c r="C41">
-        <v>7.453739146448647E-08</v>
+        <v>1.09804427134163E-07</v>
       </c>
       <c r="D41">
-        <v>2.009705278785619E-07</v>
+        <v>2.889919648540436E-07</v>
       </c>
       <c r="E41">
-        <v>4.026338402910332E-07</v>
+        <v>5.509326966154538E-07</v>
       </c>
       <c r="F41">
-        <v>1.165420714612654E-06</v>
+        <v>1.511121287745836E-06</v>
       </c>
       <c r="G41">
-        <v>3.541702587078984E-06</v>
+        <v>5.010263621895637E-06</v>
       </c>
       <c r="H41">
-        <v>1.777855941037073</v>
+        <v>1.103630921328999</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-1.716002542608108E-08</v>
+        <v>-2.504753677074213E-08</v>
       </c>
       <c r="C42">
-        <v>-1.570548154538005E-08</v>
+        <v>-2.313991074722944E-08</v>
       </c>
       <c r="D42">
-        <v>-4.168119236260413E-08</v>
+        <v>-6.002880537342019E-08</v>
       </c>
       <c r="E42">
-        <v>-8.421028288189534E-08</v>
+        <v>-1.156648410219566E-07</v>
       </c>
       <c r="F42">
-        <v>-2.421893210797199E-07</v>
+        <v>-3.151148962453768E-07</v>
       </c>
       <c r="G42">
-        <v>-6.925305002539555E-07</v>
+        <v>-9.848311177613162E-07</v>
       </c>
       <c r="H42">
-        <v>-0.3137398214231504</v>
+        <v>-0.1947591986704009</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1603,25 +1603,25 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>0.5431933148428294</v>
+        <v>0.5383614144289455</v>
       </c>
       <c r="C43">
-        <v>1.692590492552457</v>
+        <v>1.758492913050411</v>
       </c>
       <c r="D43">
-        <v>1.750704711913107</v>
+        <v>1.823315537144264</v>
       </c>
       <c r="E43">
-        <v>2.061674055019434</v>
+        <v>2.158611554173031</v>
       </c>
       <c r="F43">
-        <v>2.100362719906001</v>
+        <v>2.182473194392201</v>
       </c>
       <c r="G43">
-        <v>1.634206704291339</v>
+        <v>1.743165700217013</v>
       </c>
       <c r="H43">
-        <v>-0.4983497870354524</v>
+        <v>-0.6054139910313782</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1629,25 +1629,25 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>-0.7964189246360928</v>
+        <v>-0.7915388265828048</v>
       </c>
       <c r="C44">
-        <v>-2.54252299973095</v>
+        <v>-2.543337139778603</v>
       </c>
       <c r="D44">
-        <v>-2.636545913885381</v>
+        <v>-2.63815921588303</v>
       </c>
       <c r="E44">
-        <v>-2.774346312600874</v>
+        <v>-2.791882142889487</v>
       </c>
       <c r="F44">
-        <v>-2.920463392698956</v>
+        <v>-2.92555028452421</v>
       </c>
       <c r="G44">
-        <v>-2.961715010102143</v>
+        <v>-2.995603459174315</v>
       </c>
       <c r="H44">
-        <v>-3.109453730147962</v>
+        <v>-3.117395938358752</v>
       </c>
     </row>
   </sheetData>
